--- a/AAII_Financials/Quarterly/PLTR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PLTR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="92">
   <si>
     <t>PLTR</t>
   </si>
@@ -656,416 +656,429 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>1935500</v>
+      </c>
+      <c r="E8" s="3">
         <v>1632600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1406800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1181100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1003700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>883900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>827500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>725500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>678100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>634300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>608400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>558200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>533300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>525200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>508600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>477900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>473000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>446400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>432900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>392100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>375600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>341200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>322100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>289400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>481200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>229300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>229400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>190500</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>176300</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>146300</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>296900</v>
+      </c>
+      <c r="E9" s="3">
         <v>215800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>216000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>207300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>192900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>173000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>174500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>146600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>128600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>116300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>108600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>107900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>106900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>107600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>104300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>107600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>102200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>94400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>87600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>86800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>90900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>74100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>70500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>149300</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>132700</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>64300</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>75900</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>65100</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>56600</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>44800</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>1638600</v>
+      </c>
+      <c r="E10" s="3">
         <v>1416800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1190800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>973800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>810800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>710900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>653000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>578900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>549600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>518100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>499700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>450200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>426400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>417500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>404300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>370300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>370800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>352000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>345300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>305300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>284700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>267100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>251600</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>140100</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>348500</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>165000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>153500</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>125400</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>119700</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>101500</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1098,100 +1111,104 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>192500</v>
+      </c>
+      <c r="E12" s="3">
         <v>161000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>143600</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>144200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>135000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>134900</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>171500</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>117600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>108800</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>110000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>109300</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>105700</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>99500</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>90100</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>82000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>100900</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>88200</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>88600</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>84200</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>94300</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>110500</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>98500</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>94100</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>313900</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>152600</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>65800</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>75800</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>75900</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>78700</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>75100</v>
       </c>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1282,53 +1299,56 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E14" s="3">
+      <c r="D14" s="3">
+        <v>-66000</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3">
         <v>16200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>6000</v>
       </c>
-      <c r="G14" s="3">
-        <v>-12600</v>
-      </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3">
         <v>-6700</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>5400</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>6600</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>12400</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>1400</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>700</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>600</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>8500</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
@@ -1338,8 +1358,8 @@
       <c r="T14" s="3">
         <v>0</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>3</v>
+      <c r="U14" s="3">
+        <v>0</v>
       </c>
       <c r="V14" s="3" t="s">
         <v>3</v>
@@ -1356,12 +1376,12 @@
       <c r="Z14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AA14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB14" s="3">
         <v>700</v>
       </c>
-      <c r="AB14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1374,53 +1394,56 @@
       <c r="AF14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E15" s="3">
         <v>6800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>7000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>6000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>6500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>6600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>7000</v>
-      </c>
-      <c r="J15" s="3">
-        <v>8100</v>
       </c>
       <c r="K15" s="3">
         <v>8100</v>
       </c>
       <c r="L15" s="3">
+        <v>8100</v>
+      </c>
+      <c r="M15" s="3">
         <v>8400</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>8000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>8700</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>8400</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>8300</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1466,8 +1489,11 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1497,86 +1523,87 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1023500</v>
+      </c>
+      <c r="E17" s="3">
         <v>878600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>831400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>787800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>734400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>707800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>816500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>612400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>572800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>553500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>542600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>518200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>523200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>521100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>526500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>540100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>514800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>485800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>491800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>484100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>521800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>455200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>478700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1137100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>650500</v>
       </c>
-      <c r="AB17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1589,86 +1616,89 @@
       <c r="AF17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>912000</v>
+      </c>
+      <c r="E18" s="3">
         <v>754000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>575400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>393300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>269300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>176000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>11000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>113100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>105300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>80900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>65800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>40000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>10100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>4100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-17900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-62200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-41800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-39400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-58900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-92000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-146200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-114000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-156600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-847700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-169300</v>
       </c>
-      <c r="AB18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1681,8 +1711,11 @@
       <c r="AF18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1715,86 +1748,87 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-25800</v>
+      </c>
+      <c r="E20" s="3">
         <v>-68200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-33500</v>
       </c>
-      <c r="G20" s="3">
-        <v>6000</v>
-      </c>
       <c r="H20" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="I20" s="3">
         <v>3200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-8100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>2700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>4600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>2700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-3800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>9700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-4400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>57400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-59500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-134300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-59400</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-63700</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-8100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>2500</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-4500</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>2400</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-12000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>18400</v>
       </c>
-      <c r="AB20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1807,86 +1841,89 @@
       <c r="AF20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>946100</v>
+      </c>
+      <c r="E21" s="3">
         <v>829000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>581900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>432700</v>
       </c>
-      <c r="G21" s="3">
-        <v>269800</v>
-      </c>
       <c r="H21" s="3">
+        <v>282400</v>
+      </c>
+      <c r="I21" s="3">
         <v>179500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>26100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>118500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>108800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>88200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>71000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>52500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>8700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>16800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>46900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-115800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-171200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-94500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-118700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-97000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-138900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-115300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-150600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-857300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-143200</v>
       </c>
-      <c r="AB21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1899,8 +1936,11 @@
       <c r="AF21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1943,17 +1983,17 @@
       <c r="P22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="Q22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R22" s="3">
         <v>1700</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>1100</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>700</v>
-      </c>
-      <c r="T22" s="3">
-        <v>600</v>
       </c>
       <c r="U22" s="3">
         <v>600</v>
@@ -1965,218 +2005,227 @@
         <v>600</v>
       </c>
       <c r="X22" s="3">
-        <v>1800</v>
+        <v>600</v>
       </c>
       <c r="Y22" s="3">
         <v>1800</v>
       </c>
       <c r="Z22" s="3">
+        <v>1800</v>
+      </c>
+      <c r="AA22" s="3">
         <v>2100</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>10200</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>4600</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>2700</v>
-      </c>
-      <c r="AD22" s="3">
-        <v>200</v>
       </c>
       <c r="AE22" s="3">
         <v>200</v>
       </c>
       <c r="AF22" s="3">
+        <v>200</v>
+      </c>
+      <c r="AG22" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1081300</v>
+      </c>
+      <c r="E23" s="3">
         <v>888600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>621400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>480500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>332200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>223300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>80500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>157200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>140800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>110700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>106200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>80000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>30000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>20800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>37800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-122800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-176700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-99400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-123200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-100700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-144200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-120400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-155900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-861900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-161200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-51700</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-155400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-137800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-132700</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-141300</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>15400</v>
+      </c>
+      <c r="E24" s="3">
         <v>12200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>9800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>3800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>3600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>5600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>3600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>7800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>5200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>4700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>9300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>6500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>2200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>4400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>1100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>2600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>2000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>33000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>1400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-5700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>3100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-7600</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-8500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>3500</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>2600</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>3900</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>2000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>1400</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>5100</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2267,86 +2316,89 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1066000</v>
+      </c>
+      <c r="E26" s="3">
         <v>876400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>611600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>476700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>328600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>217700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>76900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>149300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>135600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>106100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>96900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>73400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>27900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>19200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>33500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-123900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-179300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-101400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-156200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-102100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-138600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-123500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-148300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-853300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-164700</v>
       </c>
-      <c r="AB26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC26" s="3" t="s">
         <v>3</v>
       </c>
@@ -2359,86 +2411,89 @@
       <c r="AF26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1061900</v>
+      </c>
+      <c r="E27" s="3">
         <v>870500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>608700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>475600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>326700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>214000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>79000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>143500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>134100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>105500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>93400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>71500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>28100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>16800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>30900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-123900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-179300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-101400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-156200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-102100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-138600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-123500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-148300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-853300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-170200</v>
       </c>
-      <c r="AB27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2451,8 +2506,11 @@
       <c r="AF27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2543,8 +2601,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2635,8 +2696,11 @@
       <c r="AF29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2727,8 +2791,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2819,86 +2886,89 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>25800</v>
+      </c>
+      <c r="E32" s="3">
         <v>68200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>33500</v>
       </c>
-      <c r="G32" s="3">
-        <v>-6000</v>
-      </c>
       <c r="H32" s="3">
+        <v>6600</v>
+      </c>
+      <c r="I32" s="3">
         <v>-3200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>8100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-2700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-4600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-2700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>3800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-9700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>4400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-57400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>59500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>134300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>59400</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>63700</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>8100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-2500</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>4500</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-2400</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>12000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-18400</v>
       </c>
-      <c r="AB32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2911,86 +2981,89 @@
       <c r="AF32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1061900</v>
+      </c>
+      <c r="E33" s="3">
         <v>870500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>608700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>475600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>326700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>214000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>79000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>143500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>134100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>105500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>93400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>71500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>28100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>16800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>30900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-123900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-179300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-101400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-156200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-102100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-138600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-123500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-148300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-853300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-170200</v>
       </c>
-      <c r="AB33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC33" s="3" t="s">
         <v>3</v>
       </c>
@@ -3003,8 +3076,11 @@
       <c r="AF33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3095,86 +3171,89 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1061900</v>
+      </c>
+      <c r="E35" s="3">
         <v>870500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>608700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>475600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>326700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>214000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>79000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>143500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>134100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>105500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>93400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>71500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>28100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>16800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>30900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-123900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-179300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-101400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-156200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-102100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-138600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-123500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-148300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-853300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-170200</v>
       </c>
-      <c r="AB35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC35" s="3" t="s">
         <v>3</v>
       </c>
@@ -3187,105 +3266,111 @@
       <c r="AF35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3318,8 +3403,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3352,86 +3438,87 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2030000</v>
+      </c>
+      <c r="E41" s="3">
         <v>2291600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1423800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1616000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>929500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>993500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2098500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>768700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>512700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>520400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>831000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1040300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1055900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1264700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>2598500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>2411300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>2358400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>2269400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>2290700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>2335100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>2341200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>2339400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>2011300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1800200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1497600</v>
       </c>
-      <c r="AB41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3444,71 +3531,74 @@
       <c r="AF41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>7379100</v>
+      </c>
+      <c r="E42" s="3">
         <v>5734800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>5753200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>4821900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>5070900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>4437200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>3131500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>3795900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>3485800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>3347500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>2843100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>2243300</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>2047300</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>1639800</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>35100</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>57300</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>99200</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>252600</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>234200</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>148100</v>
       </c>
-      <c r="W42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3524,8 +3614,8 @@
       <c r="AB42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC42" s="3">
-        <v>0</v>
+      <c r="AC42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD42" s="3">
         <v>0</v>
@@ -3536,86 +3626,89 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1485200</v>
+      </c>
+      <c r="E43" s="3">
         <v>1405600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1042100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1005900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>747500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>725200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>575000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>668100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>659300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>487000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>364800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>430300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>375800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>254000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>258300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>343300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>265800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>256600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>190900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>174400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>243000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>151400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>156900</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>162300</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>106100</v>
       </c>
-      <c r="AB43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3628,8 +3721,11 @@
       <c r="AF43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3672,8 +3768,8 @@
       <c r="P44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -3720,8 +3816,11 @@
       <c r="AF44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3764,42 +3863,42 @@
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="Q45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R45" s="3">
         <v>149600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>134700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>179000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>148800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>147500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>153900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>78400</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>98900</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>89200</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>432000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>76500</v>
       </c>
-      <c r="AB45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3812,86 +3911,89 @@
       <c r="AF45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>11099500</v>
+      </c>
+      <c r="E46" s="3">
         <v>9551700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>8358200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>7586200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>6890400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>6282600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>5934300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>5352000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>4773500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>4436100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>4138600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>3809400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>3576900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>3256100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>3041600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>2946600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>2902400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>2927400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>2863300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>2811500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>2662600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>2589700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>2257400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>2394400</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1680200</v>
       </c>
-      <c r="AB46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3904,52 +4006,55 @@
       <c r="AF46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>167000</v>
+      </c>
+      <c r="E47" s="3">
         <v>245000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>170000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>163200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>122900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>104500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>64900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>52600</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M47" s="3">
+      <c r="M47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N47" s="3">
         <v>32600</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O47" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
+      <c r="Q47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R47" s="3">
         <v>0</v>
@@ -3975,15 +4080,15 @@
       <c r="Y47" s="3">
         <v>0</v>
       </c>
-      <c r="Z47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA47" s="3">
+      <c r="Z47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB47" s="3">
         <v>25300</v>
       </c>
-      <c r="AB47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3996,85 +4101,88 @@
       <c r="AF47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>291700</v>
+      </c>
+      <c r="E48" s="3">
         <v>284700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>252100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>250000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>247000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>249000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>240400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>251900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>256900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>220600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>230600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>240300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>253800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>273100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>269400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>257200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>259100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>266800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>248200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>249600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>234100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>240700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>246600</v>
-      </c>
-      <c r="Z48" s="3">
-        <v>29400</v>
       </c>
       <c r="AA48" s="3">
         <v>29400</v>
       </c>
-      <c r="AB48" s="3" t="s">
-        <v>3</v>
+      <c r="AB48" s="3">
+        <v>29400</v>
       </c>
       <c r="AC48" s="3" t="s">
         <v>3</v>
@@ -4088,8 +4196,11 @@
       <c r="AF48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4121,19 +4232,19 @@
         <v>0</v>
       </c>
       <c r="M49" s="3">
+        <v>0</v>
+      </c>
+      <c r="N49" s="3">
         <v>25900</v>
       </c>
-      <c r="N49" s="3">
-        <v>0</v>
-      </c>
       <c r="O49" s="3">
         <v>0</v>
       </c>
       <c r="P49" s="3">
         <v>0</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>3</v>
+      <c r="Q49" s="3">
+        <v>0</v>
       </c>
       <c r="R49" s="3" t="s">
         <v>3</v>
@@ -4147,8 +4258,8 @@
       <c r="U49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V49" s="3">
-        <v>0</v>
+      <c r="V49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W49" s="3">
         <v>0</v>
@@ -4180,8 +4291,11 @@
       <c r="AF49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4272,8 +4386,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4364,86 +4481,89 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>120400</v>
+      </c>
+      <c r="E52" s="3">
         <v>117800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>120200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>114600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>105400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>100800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>101300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>111600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>161400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>150400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>94700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>143700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>149600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>153900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>150300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>115000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>120800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>125100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>136000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>163200</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>179000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>183800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>186500</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>179900</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>157500</v>
       </c>
-      <c r="AB52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4456,8 +4576,11 @@
       <c r="AF52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4548,86 +4671,89 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>11678600</v>
+      </c>
+      <c r="E54" s="3">
         <v>10199200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>8900400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>8114000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>7365700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>6736900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>6340900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>5768100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>5191900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>4807100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>4522400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>4193400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>3980300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>3683100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>3461200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>3318800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>3282300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>3319200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>3247500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>3224300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>3075700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>3014200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>2690500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>2603700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1892400</v>
       </c>
-      <c r="AB54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4640,8 +4766,11 @@
       <c r="AF54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4674,8 +4803,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4708,86 +4838,87 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E57" s="3">
         <v>69300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>8100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>67500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>10800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>27000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>67300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>35600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>12100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>9500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>4600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>4500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>44800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>59500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>56800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>27500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>74900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>17700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>30900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>17200</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>16400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>22200</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>16100</v>
       </c>
-      <c r="AB57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4800,8 +4931,11 @@
       <c r="AF57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4809,44 +4943,44 @@
         <v>0</v>
       </c>
       <c r="E58" s="3">
+        <v>0</v>
+      </c>
+      <c r="F58" s="3">
         <v>45900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>46300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>45500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>44400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>44000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>47600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>44100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>54100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>54200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>52200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>51900</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>53100</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
       <c r="R58" s="3">
         <v>0</v>
       </c>
@@ -4892,86 +5026,89 @@
       <c r="AF58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1388400</v>
+      </c>
+      <c r="E59" s="3">
         <v>1193800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>766000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>684900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>703500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>549600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>524900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>635500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>540400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>488800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>504000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>489000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>483600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>419700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>543200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>628800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>608900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>641700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>585200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>663900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>651700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>650400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>587500</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>920000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>588000</v>
       </c>
-      <c r="AB59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4984,86 +5121,89 @@
       <c r="AF59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1535600</v>
+      </c>
+      <c r="E60" s="3">
         <v>1382900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1175600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1180400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1089600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>967400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>996000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>943500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>806900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>750600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>746000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>688900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>685400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>601400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>587900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>688400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>665700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>669100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>660100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>681500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>682600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>667600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>603800</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>942200</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>604100</v>
       </c>
-      <c r="AB60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC60" s="3" t="s">
         <v>3</v>
       </c>
@@ -5076,53 +5216,56 @@
       <c r="AF60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>211400</v>
+      </c>
+      <c r="E61" s="3">
         <v>212000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>183500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>189200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>192300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>200200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>195200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>207300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>214300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>163000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>175200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>184100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>194100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>206400</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
@@ -5142,20 +5285,20 @@
         <v>0</v>
       </c>
       <c r="X61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y61" s="3">
         <v>198200</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>198000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>197800</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>297600</v>
       </c>
-      <c r="AB61" s="3">
-        <v>0</v>
-      </c>
       <c r="AC61" s="3">
         <v>0</v>
       </c>
@@ -5168,86 +5311,89 @@
       <c r="AF61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>13000</v>
+      </c>
+      <c r="E62" s="3">
         <v>6800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>7100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>12200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>13500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>14000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>15300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>18200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>17200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>11600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>12200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>13600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>15200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>17700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>230900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>243900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>267800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>285300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>296400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>294800</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>324100</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>342400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>366200</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>212000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>261300</v>
       </c>
-      <c r="AB62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC62" s="3" t="s">
         <v>3</v>
       </c>
@@ -5260,8 +5406,11 @@
       <c r="AF62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5352,8 +5501,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5444,8 +5596,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5536,86 +5691,89 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1793700</v>
+      </c>
+      <c r="E66" s="3">
         <v>1642900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1412400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1425700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1340100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1217900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1246500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1176700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1054100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>945900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>961500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>921500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>945100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>879900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>895900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>932200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>933500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>954400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>956400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>976300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1006700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1208200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1168000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1352000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1163000</v>
       </c>
-      <c r="AB66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5628,8 +5786,11 @@
       <c r="AF66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5662,8 +5823,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5754,8 +5916,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5846,8 +6011,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5921,11 +6089,11 @@
         <v>0</v>
       </c>
       <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB70" s="3">
         <v>2128100</v>
       </c>
-      <c r="AB70" s="3">
-        <v>0</v>
-      </c>
       <c r="AC70" s="3">
         <v>0</v>
       </c>
@@ -5938,8 +6106,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6030,86 +6201,89 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1630000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-2691900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-3562400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-4171100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-4646700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-4973400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-5187400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-5266400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-5410000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-5544100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-5649600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-5743000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-5814500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-5842600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-5859400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-5890300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-5766400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-5587100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-5485700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-5329500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-5227400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-5088800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-4965400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-4817000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-3963700</v>
       </c>
-      <c r="AB72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC72" s="3" t="s">
         <v>3</v>
       </c>
@@ -6122,8 +6296,11 @@
       <c r="AF72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6214,8 +6391,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6306,8 +6486,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6398,86 +6581,89 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>9774200</v>
+      </c>
+      <c r="E76" s="3">
         <v>8449700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>7387300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>6590500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>5928900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>5424200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>5003300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4498100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4050500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3775200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3475600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3190000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2955500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>2723700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>2565300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>2386600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>2348800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>2364700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>2291000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>2248100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>2069000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1805900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1522600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1251800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>-1398700</v>
       </c>
-      <c r="AB76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6490,8 +6676,11 @@
       <c r="AF76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6582,183 +6771,189 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1061900</v>
+      </c>
+      <c r="E81" s="3">
         <v>870500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>608700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>475600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>326700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>214000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>79000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>143500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>134100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>105500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>93400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>71500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>28100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>16800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>30900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-123900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-179300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-101400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-156200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-102100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-138600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-123500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-148300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-853300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-170200</v>
       </c>
-      <c r="AB81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC81" s="3" t="s">
         <v>3</v>
       </c>
@@ -6771,8 +6966,11 @@
       <c r="AF81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6805,86 +7003,87 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>6500</v>
+      </c>
+      <c r="E83" s="3">
         <v>6600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>7000</v>
-      </c>
-      <c r="F83" s="3">
-        <v>8100</v>
       </c>
       <c r="G83" s="3">
         <v>8100</v>
       </c>
       <c r="H83" s="3">
+        <v>8100</v>
+      </c>
+      <c r="I83" s="3">
         <v>8400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>8000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>8700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>8400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>8300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>7400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>5900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>4900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>4300</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>7400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>5900</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>4900</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>4300</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>3800</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>3100</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>4800</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>3200</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>3600</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>2500</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>7800</v>
       </c>
-      <c r="AB83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC83" s="3" t="s">
         <v>3</v>
       </c>
@@ -6897,8 +7096,11 @@
       <c r="AF83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6989,8 +7191,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7081,8 +7286,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7173,8 +7381,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7265,8 +7476,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7357,86 +7571,89 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1216200</v>
+      </c>
+      <c r="E89" s="3">
         <v>899200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>777300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>507700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>539300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>310300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>460300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>419800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>144200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>129600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>301200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>133400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>90200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>187400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>78800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>47100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>62400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>35500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>93400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>100800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>22800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>116900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-18300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-52000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-226300</v>
       </c>
-      <c r="AB89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC89" s="3" t="s">
         <v>3</v>
       </c>
@@ -7449,8 +7666,11 @@
       <c r="AF89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7483,86 +7703,87 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-14600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-7400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-13300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-6800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-7600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-6200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-3100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-4000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-4900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-3900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-4800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-4900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-14400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-5500</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-15200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-5800</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-5400</v>
-      </c>
-      <c r="W91" s="3">
-        <v>-700</v>
       </c>
       <c r="X91" s="3">
         <v>-700</v>
       </c>
       <c r="Y91" s="3">
+        <v>-700</v>
+      </c>
+      <c r="Z91" s="3">
         <v>-4800</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-1500</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-5900</v>
       </c>
-      <c r="AB91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC91" s="3" t="s">
         <v>3</v>
       </c>
@@ -7575,8 +7796,11 @@
       <c r="AF91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7667,8 +7891,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7759,86 +7986,89 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1482900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-26700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-957800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>181600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-617000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1390300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>640200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-320700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-148900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-511200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-569200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-196300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-391100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1554600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>73100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-27300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>5300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-96500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-181900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-214600</v>
-      </c>
-      <c r="W94" s="3">
-        <v>-700</v>
       </c>
       <c r="X94" s="3">
         <v>-700</v>
       </c>
       <c r="Y94" s="3">
+        <v>-700</v>
+      </c>
+      <c r="Z94" s="3">
         <v>-4900</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-4300</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-5700</v>
       </c>
-      <c r="AB94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC94" s="3" t="s">
         <v>3</v>
       </c>
@@ -7851,8 +8081,11 @@
       <c r="AF94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7885,8 +8118,9 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7929,8 +8163,8 @@
       <c r="P96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -7977,8 +8211,11 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8069,8 +8306,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8161,8 +8401,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8253,86 +8496,89 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E100" s="3">
         <v>3400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-10900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>6400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>6500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-28900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>238700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>151400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-2000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>75200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>51200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>50900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>90700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>26000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>14200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>24000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>20600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>27200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>32500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>99300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-31400</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>206400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>219100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>350100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>467300</v>
       </c>
-      <c r="AB100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC100" s="3" t="s">
         <v>3</v>
       </c>
@@ -8345,86 +8591,89 @@
       <c r="AF100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>7500</v>
+      </c>
+      <c r="E101" s="3">
         <v>4000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-7700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>5900</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-900</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-4000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>5000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-4500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>2700</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>8600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-6100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-5600</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-700</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>8600</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-6100</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-5600</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-700</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-300</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-2100</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>700</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-2200</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>1900</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-500</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-200</v>
       </c>
-      <c r="AB101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC101" s="3" t="s">
         <v>3</v>
       </c>
@@ -8437,86 +8686,89 @@
       <c r="AF101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-261500</v>
+      </c>
+      <c r="E102" s="3">
         <v>873400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-193400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>693600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-63800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1104900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>1331500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>256400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-7600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-310400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-211800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-12100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-214800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-1338600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>174600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>37600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>82700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-34500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-56300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-16600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-8700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>320300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>197800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>293300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>235100</v>
       </c>
-      <c r="AB102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC102" s="3" t="s">
         <v>3</v>
       </c>
@@ -8527,6 +8779,9 @@
         <v>3</v>
       </c>
       <c r="AF102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
